--- a/tasks/AnalyticalCase/bin/output/StdDevEmployeeHours.xlsx
+++ b/tasks/AnalyticalCase/bin/output/StdDevEmployeeHours.xlsx
@@ -427,7 +427,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>3.3266583166227868</v>
+        <v>3.326658316622788</v>
       </c>
     </row>
     <row r="9">
@@ -507,7 +507,7 @@
         <v>18</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>3.5726550351244377</v>
+        <v>3.572655035124438</v>
       </c>
     </row>
     <row r="19">
@@ -699,7 +699,7 @@
         <v>42</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>0.9239889369227076</v>
+        <v>0.9239889369227073</v>
       </c>
     </row>
     <row r="43">
@@ -907,7 +907,7 @@
         <v>68</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>4.008492720323798</v>
+        <v>4.008492720323797</v>
       </c>
     </row>
     <row r="69">
@@ -1067,7 +1067,7 @@
         <v>88</v>
       </c>
       <c r="B88" t="n" s="0">
-        <v>1.602269224152628</v>
+        <v>1.6022692241526297</v>
       </c>
     </row>
     <row r="89">
